--- a/backend/excel/employees.xlsx
+++ b/backend/excel/employees.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,180 +533,6 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>2026-10-07 18:58:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>emp_3dbe82c7aa1d</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>jeeva</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>jeeva@gmail.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$ExSptH1qz5OHtr12$66de4ab50187130e318b82f4ac7dd1c5b4fcb275888349f2da4bf4dcd7057b85105f79b97f0547dda3b6c62db7a6800eda8129f5097ef1cc2e866b522ab69194</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>+91 2345667777</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-10-07 15:40:10</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-10-07 15:40:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>emp_3cb8aea00a2d</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>vijay</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>vijay@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$7brWV9AShRZLu2do$b8b75dfd61475eb7c1bb0b27d81c230136ca7672ba67f4cf7ea639114ed8551692ce061470d330afff53112de922b076623e42024e0eb5539208eea17b21d672</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>marketing</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:24:31</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:24:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>emp_20205e6cffa7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>logesh</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>logesh@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$58LsQDPhNYe5GI2l$ce94b63bf9017520f3a29176e37c5f5d8de1b6e7906962e75b4dc300fdc373349e33ab957f75659dfd5ea5f70612b661ecb9ef7d91b2f2ced0b3e2064a41888d</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>+91 2345667777</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Java Developer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>website creating</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:48:47</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-10-07 16:48:47</t>
         </is>
       </c>
     </row>

--- a/backend/excel/employees.xlsx
+++ b/backend/excel/employees.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$XEqFyJPIBboLFdGG$ae470ff552165e5195c339a944ffb7776d37f6edd5d09205de61521e2f540caf7c6e5f5c14bad54bfbbb8fc93949ea9dff348624dfc08128d362ada40c003caa</t>
+          <t>scrypt:32768:8:1$abZVgLrc5Payvhaf$a0d34a07dbf3098cbb0a5663fe30551cc5a42e9949696949f1f6c282ba8c6f52c5dfc8cd85cd70679d4dfa6645a0b8dddb4df4d7b296307089e7fe2c7589cadd</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-07 18:58:35</t>
+          <t>2026-10-09 16:59:47</t>
         </is>
       </c>
     </row>
